--- a/excel/Indemo.xlsx
+++ b/excel/Indemo.xlsx
@@ -5,15 +5,15 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Indemo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evald\OneDrive\Dokumentai\portfolio-analytics\portfolio-v2\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8448A1-4614-4BAA-950F-216CA5005144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA128F4-A33B-4818-8465-918788DA7BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Overwiev" sheetId="33" r:id="rId1"/>
+    <sheet name="Overview" sheetId="33" r:id="rId1"/>
     <sheet name="Pinigai" sheetId="127" r:id="rId2"/>
     <sheet name="J035" sheetId="144" r:id="rId3"/>
     <sheet name="J036" sheetId="145" r:id="rId4"/>
@@ -1170,21 +1170,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="117">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="115">
     <dxf>
       <fill>
         <patternFill>
@@ -7312,7 +7298,7 @@
       </c>
       <c r="T3" s="6">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.15173498988151554</v>
+        <v>0.14528587460517886</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -10518,7 +10504,7 @@
     <mergeCell ref="K1:N1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:I89">
-    <cfRule type="expression" dxfId="116" priority="1">
+    <cfRule type="expression" dxfId="114" priority="1">
       <formula>$C3=$G3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11238,7 +11224,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="108" priority="1">
+    <cfRule type="expression" dxfId="106" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11870,7 +11856,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="107" priority="1">
+    <cfRule type="expression" dxfId="105" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12530,7 +12516,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="106" priority="1">
+    <cfRule type="expression" dxfId="104" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13194,7 +13180,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="105" priority="1">
+    <cfRule type="expression" dxfId="103" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13866,7 +13852,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="104" priority="1">
+    <cfRule type="expression" dxfId="102" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14538,7 +14524,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="103" priority="1">
+    <cfRule type="expression" dxfId="101" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15202,7 +15188,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="102" priority="1">
+    <cfRule type="expression" dxfId="100" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15795,7 +15781,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="101" priority="1">
+    <cfRule type="expression" dxfId="99" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16451,7 +16437,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="100" priority="1">
+    <cfRule type="expression" dxfId="98" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17083,7 +17069,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="99" priority="1">
+    <cfRule type="expression" dxfId="97" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17161,7 +17147,7 @@
       </c>
       <c r="I2" s="6">
         <f ca="1">XIRR(K2:K200,A2:A200)</f>
-        <v>0.15173498988151554</v>
+        <v>0.14528587460517886</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="5">
@@ -18855,7 +18841,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="24">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46232</v>
       </c>
       <c r="B200" s="27"/>
       <c r="C200" s="27"/>
@@ -18867,7 +18853,7 @@
         <v>615.37</v>
       </c>
       <c r="K200" s="5">
-        <f>Overwiev!Q3</f>
+        <f>Overview!Q3</f>
         <v>626.72</v>
       </c>
     </row>
@@ -19523,7 +19509,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="98" priority="1">
+    <cfRule type="expression" dxfId="96" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20171,7 +20157,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="97" priority="1">
+    <cfRule type="expression" dxfId="95" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20811,7 +20797,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="96" priority="1">
+    <cfRule type="expression" dxfId="94" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21443,7 +21429,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="95" priority="1">
+    <cfRule type="expression" dxfId="93" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22083,7 +22069,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="94" priority="1">
+    <cfRule type="expression" dxfId="92" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22755,7 +22741,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="93" priority="1">
+    <cfRule type="expression" dxfId="91" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23387,7 +23373,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="92" priority="1">
+    <cfRule type="expression" dxfId="90" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24251,7 +24237,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="91" priority="1">
+    <cfRule type="expression" dxfId="89" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25019,7 +25005,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="90" priority="1">
+    <cfRule type="expression" dxfId="88" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25771,7 +25757,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="89" priority="1">
+    <cfRule type="expression" dxfId="87" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26029,7 +26015,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="115" priority="1">
+    <cfRule type="expression" dxfId="113" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26773,7 +26759,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="88" priority="1">
+    <cfRule type="expression" dxfId="86" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27517,7 +27503,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="87" priority="1">
+    <cfRule type="expression" dxfId="85" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28269,7 +28255,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="86" priority="1">
+    <cfRule type="expression" dxfId="84" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29013,7 +28999,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="85" priority="1">
+    <cfRule type="expression" dxfId="83" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29765,7 +29751,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="84" priority="1">
+    <cfRule type="expression" dxfId="82" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30533,7 +30519,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="83" priority="1">
+    <cfRule type="expression" dxfId="81" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31325,7 +31311,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="82" priority="1">
+    <cfRule type="expression" dxfId="80" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32093,7 +32079,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="81" priority="1">
+    <cfRule type="expression" dxfId="79" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32837,7 +32823,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="80" priority="1">
+    <cfRule type="expression" dxfId="78" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33661,7 +33647,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="79" priority="1">
+    <cfRule type="expression" dxfId="77" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33919,7 +33905,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="114" priority="1">
+    <cfRule type="expression" dxfId="112" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34663,7 +34649,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="78" priority="1">
+    <cfRule type="expression" dxfId="76" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35423,7 +35409,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="77" priority="1">
+    <cfRule type="expression" dxfId="75" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36175,7 +36161,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="76" priority="1">
+    <cfRule type="expression" dxfId="74" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36860,7 +36846,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="75" priority="1">
+    <cfRule type="expression" dxfId="73" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -37612,7 +37598,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="74" priority="1">
+    <cfRule type="expression" dxfId="72" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38372,7 +38358,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="73" priority="1">
+    <cfRule type="expression" dxfId="71" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39282,7 +39268,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="72" priority="1">
+    <cfRule type="expression" dxfId="70" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -40168,7 +40154,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="71" priority="1">
+    <cfRule type="expression" dxfId="69" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41038,7 +41024,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="70" priority="1">
+    <cfRule type="expression" dxfId="68" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41932,7 +41918,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="69" priority="1">
+    <cfRule type="expression" dxfId="67" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42190,7 +42176,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="113" priority="1">
+    <cfRule type="expression" dxfId="111" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43068,7 +43054,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="68" priority="1">
+    <cfRule type="expression" dxfId="66" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43858,7 +43844,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="67" priority="1">
+    <cfRule type="expression" dxfId="65" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -44648,7 +44634,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="66" priority="1">
+    <cfRule type="expression" dxfId="64" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -45446,7 +45432,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="65" priority="1">
+    <cfRule type="expression" dxfId="63" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46244,7 +46230,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="64" priority="1">
+    <cfRule type="expression" dxfId="62" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47042,7 +47028,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="63" priority="1">
+    <cfRule type="expression" dxfId="61" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47832,7 +47818,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="62" priority="1">
+    <cfRule type="expression" dxfId="60" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48646,7 +48632,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="61" priority="1">
+    <cfRule type="expression" dxfId="59" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49428,7 +49414,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="60" priority="1">
+    <cfRule type="expression" dxfId="58" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50218,7 +50204,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="59" priority="1">
+    <cfRule type="expression" dxfId="57" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50487,7 +50473,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="112" priority="1">
+    <cfRule type="expression" dxfId="110" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -51357,7 +51343,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="58" priority="1">
+    <cfRule type="expression" dxfId="56" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52080,7 +52066,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="57" priority="1">
+    <cfRule type="expression" dxfId="55" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52870,12 +52856,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="56" priority="3">
+    <cfRule type="expression" dxfId="54" priority="3">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="55" priority="1">
+    <cfRule type="expression" dxfId="53" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53689,12 +53675,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="54" priority="3">
+    <cfRule type="expression" dxfId="52" priority="3">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="53" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54484,12 +54470,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="52" priority="2">
+    <cfRule type="expression" dxfId="50" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="51" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -55279,12 +55265,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="50" priority="2">
+    <cfRule type="expression" dxfId="48" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56074,12 +56060,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="48" priority="2">
+    <cfRule type="expression" dxfId="46" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56885,12 +56871,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="46" priority="2">
+    <cfRule type="expression" dxfId="44" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -57728,12 +57714,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="44" priority="2">
+    <cfRule type="expression" dxfId="42" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -58531,12 +58517,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="42" priority="2">
+    <cfRule type="expression" dxfId="40" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -58794,7 +58780,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="111" priority="1">
+    <cfRule type="expression" dxfId="109" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -59584,12 +59570,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="40" priority="2">
+    <cfRule type="expression" dxfId="38" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -60411,12 +60397,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="38" priority="2">
+    <cfRule type="expression" dxfId="36" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61246,12 +61232,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="36" priority="2">
+    <cfRule type="expression" dxfId="34" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62097,12 +62083,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="34" priority="2">
+    <cfRule type="expression" dxfId="32" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62924,12 +62910,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="32" priority="2">
+    <cfRule type="expression" dxfId="30" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -63759,12 +63745,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="30" priority="2">
+    <cfRule type="expression" dxfId="28" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64562,12 +64548,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="28" priority="2">
+    <cfRule type="expression" dxfId="26" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65365,12 +65351,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="26" priority="2">
+    <cfRule type="expression" dxfId="24" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -66168,12 +66154,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="24" priority="2">
+    <cfRule type="expression" dxfId="22" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -66323,7 +66309,7 @@
         <v>1.84</v>
       </c>
       <c r="H4" s="7">
-        <f t="shared" ref="H4:H20" si="0">IF($B$9&gt;0,$B$9,"")</f>
+        <f t="shared" ref="H4:H6" si="0">IF($B$9&gt;0,$B$9,"")</f>
         <v>46203</v>
       </c>
       <c r="I4" s="5">
@@ -66912,7 +66898,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -67582,7 +67568,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="110" priority="1">
+    <cfRule type="expression" dxfId="108" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68372,12 +68358,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="20" priority="2">
+    <cfRule type="expression" dxfId="19" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69167,12 +69153,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="17" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69962,12 +69948,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="16" priority="2">
+    <cfRule type="expression" dxfId="15" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70757,12 +70743,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="14" priority="2">
+    <cfRule type="expression" dxfId="13" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -71552,12 +71538,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="12" priority="2">
+    <cfRule type="expression" dxfId="11" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -72347,12 +72333,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -73126,12 +73112,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -73905,12 +73891,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -74684,12 +74670,12 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>$B$7=$B$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76198,7 +76184,7 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="109" priority="1">
+    <cfRule type="expression" dxfId="107" priority="1">
       <formula>$B$10=$B$11</formula>
     </cfRule>
   </conditionalFormatting>

--- a/excel/Indemo.xlsx
+++ b/excel/Indemo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Indemo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evald\OneDrive\Dokumentai\portfolio-analytics\portfolio-dashboard-clean\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E406AABB-EAB9-4F79-9F0C-F9D035EDD623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4954635D-AEF7-4308-AA48-64F8A3D53787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="33" r:id="rId1"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="T3" s="6">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.14429696202278133</v>
+        <v>0.14164766669273374</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="I2" s="6">
         <f ca="1">XIRR(K2:K200,A2:A200)</f>
-        <v>0.14429696202278133</v>
+        <v>0.14164766669273374</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="5">
@@ -18951,7 +18951,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="24">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B200" s="26"/>
       <c r="C200" s="26"/>

--- a/excel/Indemo.xlsx
+++ b/excel/Indemo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evald\OneDrive\Dokumentai\portfolio-analytics\portfolio-dashboard-clean\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Indemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4954635D-AEF7-4308-AA48-64F8A3D53787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E406AABB-EAB9-4F79-9F0C-F9D035EDD623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="33" r:id="rId1"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="T3" s="6">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.14164766669273374</v>
+        <v>0.14429696202278133</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="I2" s="6">
         <f ca="1">XIRR(K2:K200,A2:A200)</f>
-        <v>0.14164766669273374</v>
+        <v>0.14429696202278133</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="5">
@@ -18951,7 +18951,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="24">
         <f ca="1">TODAY()</f>
-        <v>46243</v>
+        <v>46236</v>
       </c>
       <c r="B200" s="26"/>
       <c r="C200" s="26"/>
